--- a/artfynd/A 33477-2022 artfynd.xlsx
+++ b/artfynd/A 33477-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33477-2022 artfynd.xlsx
+++ b/artfynd/A 33477-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>69616473</v>
       </c>
       <c r="B2" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>684111.425272649</v>
+        <v>684111</v>
       </c>
       <c r="R2" t="n">
-        <v>6624675.403663342</v>
+        <v>6624675</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2003-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2003-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 33477-2022 artfynd.xlsx
+++ b/artfynd/A 33477-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69616473</v>
       </c>
       <c r="B2" t="n">
-        <v>99057</v>
+        <v>99058</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33477-2022 artfynd.xlsx
+++ b/artfynd/A 33477-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69616473</v>
       </c>
       <c r="B2" t="n">
-        <v>99058</v>
+        <v>99059</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33477-2022 artfynd.xlsx
+++ b/artfynd/A 33477-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69616473</v>
       </c>
       <c r="B2" t="n">
-        <v>99059</v>
+        <v>99062</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33477-2022 artfynd.xlsx
+++ b/artfynd/A 33477-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69616473</v>
       </c>
       <c r="B2" t="n">
-        <v>99062</v>
+        <v>99061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33477-2022 artfynd.xlsx
+++ b/artfynd/A 33477-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69616473</v>
       </c>
       <c r="B2" t="n">
-        <v>99061</v>
+        <v>99067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33477-2022 artfynd.xlsx
+++ b/artfynd/A 33477-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69616473</v>
       </c>
       <c r="B2" t="n">
-        <v>99067</v>
+        <v>99070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33477-2022 artfynd.xlsx
+++ b/artfynd/A 33477-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69616473</v>
       </c>
       <c r="B2" t="n">
-        <v>99070</v>
+        <v>99075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33477-2022 artfynd.xlsx
+++ b/artfynd/A 33477-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>69616473</v>
       </c>
       <c r="B2" t="n">
-        <v>99075</v>
+        <v>99077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
